--- a/data/trans_orig/VUL_MENTALCOM-Edad-trans_orig.xlsx
+++ b/data/trans_orig/VUL_MENTALCOM-Edad-trans_orig.xlsx
@@ -651,8 +651,10 @@
           <t>16-24 años</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C4" s="4" t="n">
         <v>3</v>
@@ -720,8 +722,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C5" s="4" t="n">
         <v>78</v>
@@ -864,8 +868,10 @@
           <t>25-34 años</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>4</v>
@@ -933,8 +939,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
-      <c r="B8" s="2" t="n">
-        <v>0</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>123</v>
@@ -1077,8 +1085,10 @@
           <t>35-44 años</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>14</v>
@@ -1146,8 +1156,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>255</v>
@@ -1290,8 +1302,10 @@
           <t>45-54 años</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>30</v>
@@ -1359,8 +1373,10 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
-      <c r="B14" s="2" t="n">
-        <v>0</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>313</v>
@@ -1503,8 +1519,10 @@
           <t>55-64 años</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>1</v>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>34</v>
@@ -1572,8 +1590,10 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
-      <c r="B17" s="2" t="n">
-        <v>0</v>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>320</v>
@@ -1716,8 +1736,10 @@
           <t>65-74 años</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>1</v>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C19" s="4" t="n">
         <v>10</v>
@@ -1785,8 +1807,10 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
-      <c r="B20" s="2" t="n">
-        <v>0</v>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C20" s="4" t="n">
         <v>275</v>
@@ -1929,8 +1953,10 @@
           <t>75 y más años</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>1</v>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C22" s="4" t="n">
         <v>19</v>
@@ -1998,8 +2024,10 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
-      <c r="B23" s="2" t="n">
-        <v>0</v>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C23" s="4" t="n">
         <v>182</v>
@@ -2142,8 +2170,10 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
-        <v>1</v>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C25" s="4" t="n">
         <v>114</v>
@@ -2211,8 +2241,10 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
-      <c r="B26" s="2" t="n">
-        <v>0</v>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C26" s="4" t="n">
         <v>1546</v>
@@ -2590,8 +2622,10 @@
           <t>16-24 años</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C4" s="4" t="n">
         <v>16</v>
@@ -2659,8 +2693,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C5" s="4" t="n">
         <v>147</v>
@@ -2803,8 +2839,10 @@
           <t>25-34 años</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>32</v>
@@ -2872,8 +2910,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
-      <c r="B8" s="2" t="n">
-        <v>0</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>240</v>
@@ -3016,8 +3056,10 @@
           <t>35-44 años</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>59</v>
@@ -3085,8 +3127,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>257</v>
@@ -3229,8 +3273,10 @@
           <t>45-54 años</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>52</v>
@@ -3298,8 +3344,10 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
-      <c r="B14" s="2" t="n">
-        <v>0</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>233</v>
@@ -3442,8 +3490,10 @@
           <t>55-64 años</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>1</v>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>33</v>
@@ -3511,8 +3561,10 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
-      <c r="B17" s="2" t="n">
-        <v>0</v>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>198</v>
@@ -3655,8 +3707,10 @@
           <t>65-74 años</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>1</v>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C19" s="4" t="n">
         <v>28</v>
@@ -3724,8 +3778,10 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
-      <c r="B20" s="2" t="n">
-        <v>0</v>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C20" s="4" t="n">
         <v>150</v>
@@ -3868,8 +3924,10 @@
           <t>75 y más años</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>1</v>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C22" s="4" t="n">
         <v>40</v>
@@ -3937,8 +3995,10 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
-      <c r="B23" s="2" t="n">
-        <v>0</v>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C23" s="4" t="n">
         <v>153</v>
@@ -4081,8 +4141,10 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
-        <v>1</v>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C25" s="4" t="n">
         <v>260</v>
@@ -4150,8 +4212,10 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
-      <c r="B26" s="2" t="n">
-        <v>0</v>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C26" s="4" t="n">
         <v>1378</v>
@@ -4529,8 +4593,10 @@
           <t>16-24 años</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C4" s="4" t="n">
         <v>6</v>
@@ -4598,8 +4664,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C5" s="4" t="n">
         <v>221</v>
@@ -4742,8 +4810,10 @@
           <t>25-34 años</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>8</v>
@@ -4811,8 +4881,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
-      <c r="B8" s="2" t="n">
-        <v>0</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>224</v>
@@ -4955,8 +5027,10 @@
           <t>35-44 años</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>8</v>
@@ -5024,8 +5098,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>318</v>
@@ -5168,8 +5244,10 @@
           <t>45-54 años</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>10</v>
@@ -5237,8 +5315,10 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
-      <c r="B14" s="2" t="n">
-        <v>0</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>385</v>
@@ -5381,8 +5461,10 @@
           <t>55-64 años</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>1</v>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>18</v>
@@ -5450,8 +5532,10 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
-      <c r="B17" s="2" t="n">
-        <v>0</v>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>282</v>
@@ -5594,8 +5678,10 @@
           <t>65-74 años</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>1</v>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C19" s="4" t="n">
         <v>12</v>
@@ -5663,8 +5749,10 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
-      <c r="B20" s="2" t="n">
-        <v>0</v>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C20" s="4" t="n">
         <v>455</v>
@@ -5807,8 +5895,10 @@
           <t>75 y más años</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>1</v>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C22" s="4" t="n">
         <v>23</v>
@@ -5876,8 +5966,10 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
-      <c r="B23" s="2" t="n">
-        <v>0</v>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C23" s="4" t="n">
         <v>364</v>
@@ -6020,8 +6112,10 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
-        <v>1</v>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C25" s="4" t="n">
         <v>85</v>
@@ -6089,8 +6183,10 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
-      <c r="B26" s="2" t="n">
-        <v>0</v>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C26" s="4" t="n">
         <v>2249</v>
@@ -6468,8 +6564,10 @@
           <t>16-24 años</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n">
-        <v>1</v>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C4" s="4" t="n">
         <v>7</v>
@@ -6537,8 +6635,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="n"/>
-      <c r="B5" s="2" t="n">
-        <v>0</v>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C5" s="4" t="n">
         <v>314</v>
@@ -6681,8 +6781,10 @@
           <t>25-34 años</t>
         </is>
       </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C7" s="4" t="n">
         <v>8</v>
@@ -6750,8 +6852,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n"/>
-      <c r="B8" s="2" t="n">
-        <v>0</v>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C8" s="4" t="n">
         <v>345</v>
@@ -6894,8 +6998,10 @@
           <t>35-44 años</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n">
-        <v>1</v>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C10" s="4" t="n">
         <v>10</v>
@@ -6963,8 +7069,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n"/>
-      <c r="B11" s="2" t="n">
-        <v>0</v>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C11" s="4" t="n">
         <v>460</v>
@@ -7107,8 +7215,10 @@
           <t>45-54 años</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n">
-        <v>1</v>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C13" s="4" t="n">
         <v>26</v>
@@ -7176,8 +7286,10 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="n"/>
-      <c r="B14" s="2" t="n">
-        <v>0</v>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C14" s="4" t="n">
         <v>662</v>
@@ -7320,8 +7432,10 @@
           <t>55-64 años</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n">
-        <v>1</v>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C16" s="4" t="n">
         <v>42</v>
@@ -7389,8 +7503,10 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="n"/>
-      <c r="B17" s="2" t="n">
-        <v>0</v>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C17" s="4" t="n">
         <v>578</v>
@@ -7533,8 +7649,10 @@
           <t>65-74 años</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n">
-        <v>1</v>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C19" s="4" t="n">
         <v>22</v>
@@ -7602,8 +7720,10 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="n"/>
-      <c r="B20" s="2" t="n">
-        <v>0</v>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C20" s="4" t="n">
         <v>532</v>
@@ -7746,8 +7866,10 @@
           <t>75 y más años</t>
         </is>
       </c>
-      <c r="B22" s="2" t="n">
-        <v>1</v>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C22" s="4" t="n">
         <v>21</v>
@@ -7815,8 +7937,10 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="n"/>
-      <c r="B23" s="2" t="n">
-        <v>0</v>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C23" s="4" t="n">
         <v>471</v>
@@ -7959,8 +8083,10 @@
           <t>Total</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n">
-        <v>1</v>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
       </c>
       <c r="C25" s="4" t="n">
         <v>136</v>
@@ -8028,8 +8154,10 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="n"/>
-      <c r="B26" s="2" t="n">
-        <v>0</v>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
       </c>
       <c r="C26" s="4" t="n">
         <v>3362</v>
